--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="2157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="2160">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -6489,6 +6489,15 @@
   </si>
   <si>
     <t xml:space="preserve">Public TSV match from AUTO_Public_TSV_FileList (generated by _tools/file_list.R; do not edit manually)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A9780195043716_Table12-1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A9780195043716_Table12-3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A7983368_Table2.tsv</t>
   </si>
 </sst>
 </file>
@@ -6506,42 +6515,33 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <b/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <b/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b/>
     </font>
   </fonts>
   <fills count="4">
@@ -6620,8 +6620,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -6632,12 +6630,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16999,7 +16999,7 @@
       </c>
       <c r="L111" s="6" t="str">
         <f t="array" ref="L111">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K111,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>PMID%3A7983368_Table2.tsv</v>
       </c>
     </row>
     <row r="112" ht="17" customHeight="1">
@@ -42972,7 +42972,7 @@
       </c>
       <c r="L420" s="6" t="str">
         <f t="array" ref="L420">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K420,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>ISBN%3A9780195043716_Table12-1.tsv</v>
       </c>
       <c r="M420" s="2" t="s">
         <v>1384</v>
@@ -43117,7 +43117,7 @@
       </c>
       <c r="L422" s="6" t="str">
         <f t="array" ref="L422">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K422,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>ISBN%3A9780195043716_Table12-3.tsv</v>
       </c>
       <c r="M422" s="2" t="s">
         <v>1388</v>
@@ -44009,120 +44009,120 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="8" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AB1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AC1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AD1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AE1" s="8" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="8" t="s">
+      <c r="AG1" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>1398</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="11" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="14" t="str">
+      <c r="E2" s="12" t="str">
         <f t="shared" ref="E2:E17" si="0">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A2,","), "-", ""), " ", "")</f>
         <v>Changizi</v>
       </c>
-      <c r="F2" s="14" t="str">
+      <c r="F2" s="12" t="str">
         <f t="shared" ref="F2:F17" si="1">_xlfn.LET(
 _xlpm.authors,_xlfn.TEXTBEFORE(A2," ("&amp;G2&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
@@ -44131,15 +44131,15 @@
 )</f>
         <v>He</v>
       </c>
-      <c r="G2" s="14" t="str">
+      <c r="G2" s="12" t="str">
         <f t="shared" ref="G2:G17" si="2">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, "("), ")")</f>
         <v>2005</v>
       </c>
-      <c r="H2" s="14" t="str">
+      <c r="H2" s="12" t="str">
         <f t="shared" ref="H2:H17" si="3">E2 &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "_") &amp; IF(G2&lt;&gt;"", "_" &amp; G2, "_") &amp; IF(B2&lt;&gt;"", "_" &amp; B2, "")</f>
         <v>Changizi_He_2005</v>
       </c>
-      <c r="I2" s="14" t="str">
+      <c r="I2" s="12" t="str">
         <f t="shared" ref="I2:I17" si="4">_xlfn.LET(
 _xlpm.doi,IF(C2&lt;&gt;"",C2,_xlfn.TEXTAFTER(A2,"https://doi.org/")),
 SUBSTITUTE(
@@ -44154,1295 +44154,1295 @@
 )</f>
         <v>10.1002%2Fcplx.20085</v>
       </c>
-      <c r="J2" s="14" t="str">
+      <c r="J2" s="12" t="str">
         <f t="shared" ref="J2:J17" si="5">TRIM(_xlfn.TEXTJOIN("_",FALSE(),H2,(SUBSTITUTE(SUBSTITUTE(D2," ",""), "_", ""))))</f>
         <v>Changizi_He_2005_Table1</v>
       </c>
-      <c r="K2" s="14" t="str">
+      <c r="K2" s="12" t="str">
         <f t="shared" ref="K2:K17" si="6">I2 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D2,CHAR(160),"")," ",""),"_","")</f>
         <v>10.1002%2Fcplx.20085_Table1</v>
       </c>
-      <c r="L2" s="14" t="str">
+      <c r="L2" s="12" t="str">
         <f t="array" ref="L2">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K2,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="10" t="s">
         <v>1399</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="10" t="s">
         <v>1401</v>
       </c>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12" t="s">
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10" t="s">
         <v>1402</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12" t="s">
+      <c r="U2" s="10"/>
+      <c r="V2" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W2" s="11"/>
-      <c r="X2" s="12" t="s">
+      <c r="W2" s="9"/>
+      <c r="X2" s="10" t="s">
         <v>1403</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Y2" s="10" t="s">
         <v>1403</v>
       </c>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="11" t="s">
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="9" t="s">
         <v>1404</v>
       </c>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="11" t="s">
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="8" t="s">
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="13" t="s">
         <v>1405</v>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>1398</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="11" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="14" t="str">
+      <c r="E3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Changizi</v>
       </c>
-      <c r="F3" s="14" t="str">
+      <c r="F3" s="12" t="str">
         <f t="shared" si="1"/>
         <v>He</v>
       </c>
-      <c r="G3" s="14" t="str">
+      <c r="G3" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2005</v>
       </c>
-      <c r="H3" s="14" t="str">
+      <c r="H3" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Changizi_He_2005</v>
       </c>
-      <c r="I3" s="14" t="str">
+      <c r="I3" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1002%2Fcplx.20085</v>
       </c>
-      <c r="J3" s="14" t="str">
+      <c r="J3" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Changizi_He_2005_Table2</v>
       </c>
-      <c r="K3" s="14" t="str">
+      <c r="K3" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1002%2Fcplx.20085_Table2</v>
       </c>
-      <c r="L3" s="14" t="str">
+      <c r="L3" s="12" t="str">
         <f t="array" ref="L3">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K3,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="10" t="s">
         <v>1406</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="10" t="s">
         <v>1407</v>
       </c>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12" t="s">
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10" t="s">
         <v>1402</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="T3" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U3" s="12"/>
-      <c r="V3" s="12" t="s">
+      <c r="U3" s="10"/>
+      <c r="V3" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W3" s="11"/>
-      <c r="X3" s="12" t="s">
+      <c r="W3" s="9"/>
+      <c r="X3" s="10" t="s">
         <v>1408</v>
       </c>
-      <c r="Y3" s="12" t="s">
+      <c r="Y3" s="10" t="s">
         <v>1408</v>
       </c>
-      <c r="Z3" s="12"/>
-      <c r="AA3" s="12"/>
-      <c r="AB3" s="11" t="s">
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="9" t="s">
         <v>1404</v>
       </c>
-      <c r="AC3" s="12"/>
-      <c r="AD3" s="12"/>
-      <c r="AE3" s="11" t="s">
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF3" s="11"/>
-      <c r="AG3" s="8" t="s">
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="13" t="s">
         <v>1409</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>1410</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="11" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="13" t="str">
+      <c r="E4" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Deaner</v>
       </c>
-      <c r="F4" s="13" t="str">
+      <c r="F4" s="11" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="G4" s="13" t="str">
+      <c r="G4" s="11" t="str">
         <f t="shared" si="2"/>
         <v>2007</v>
       </c>
-      <c r="H4" s="13" t="str">
+      <c r="H4" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Deaner_etal_2007</v>
       </c>
-      <c r="I4" s="13" t="str">
+      <c r="I4" s="11" t="str">
         <f t="shared" si="4"/>
         <v>10.1159%2F000102973</v>
       </c>
-      <c r="J4" s="13" t="str">
+      <c r="J4" s="11" t="str">
         <f t="shared" si="5"/>
         <v>Deaner_etal_2007_Table1</v>
       </c>
-      <c r="K4" s="13" t="str">
+      <c r="K4" s="11" t="str">
         <f t="shared" si="6"/>
         <v>10.1159%2F000102973_Table1</v>
       </c>
-      <c r="L4" s="13" t="str">
+      <c r="L4" s="11" t="str">
         <f t="array" ref="L4">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K4,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="10" t="s">
         <v>1411</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="10" t="s">
         <v>1412</v>
       </c>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12" t="s">
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10" t="s">
         <v>1413</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="S4" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="T4" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12" t="s">
+      <c r="U4" s="10"/>
+      <c r="V4" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W4" s="11" t="s">
+      <c r="W4" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X4" s="12" t="s">
+      <c r="X4" s="10" t="s">
         <v>1414</v>
       </c>
-      <c r="Y4" s="12" t="s">
+      <c r="Y4" s="10" t="s">
         <v>1414</v>
       </c>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="11" t="s">
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="9" t="s">
         <v>1415</v>
       </c>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="11" t="s">
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="8" t="s">
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="13" t="s">
         <v>1416</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="11" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="14" t="str">
+      <c r="E5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Deaner</v>
       </c>
-      <c r="F5" s="14" t="str">
+      <c r="F5" s="12" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="G5" s="14" t="str">
+      <c r="G5" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2006</v>
       </c>
-      <c r="H5" s="14" t="str">
+      <c r="H5" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Deaner_etal_2006</v>
       </c>
-      <c r="I5" s="14" t="str">
+      <c r="I5" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1177%2F147470490600400114</v>
       </c>
-      <c r="J5" s="14" t="str">
+      <c r="J5" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Deaner_etal_2006_Table2</v>
       </c>
-      <c r="K5" s="14" t="str">
+      <c r="K5" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1177%2F147470490600400114_Table2</v>
       </c>
-      <c r="L5" s="14" t="str">
+      <c r="L5" s="12" t="str">
         <f t="array" ref="L5">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K5,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="10" t="s">
         <v>1417</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="10" t="s">
         <v>1418</v>
       </c>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12" t="s">
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="T5" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12" t="s">
+      <c r="U5" s="10"/>
+      <c r="V5" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W5" s="11" t="s">
+      <c r="W5" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X5" s="12" t="s">
+      <c r="X5" s="10" t="s">
         <v>1419</v>
       </c>
-      <c r="Y5" s="12" t="s">
+      <c r="Y5" s="10" t="s">
         <v>1419</v>
       </c>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="11" t="s">
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="9" t="s">
         <v>1420</v>
       </c>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="11" t="s">
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF5" s="11"/>
-      <c r="AG5" s="8" t="s">
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="13" t="s">
         <v>1421</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="11" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="14" t="str">
+      <c r="E6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Deaner</v>
       </c>
-      <c r="F6" s="14" t="str">
+      <c r="F6" s="12" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="G6" s="14" t="str">
+      <c r="G6" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2006</v>
       </c>
-      <c r="H6" s="14" t="str">
+      <c r="H6" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Deaner_etal_2006</v>
       </c>
-      <c r="I6" s="14" t="str">
+      <c r="I6" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1177%2F147470490600400114</v>
       </c>
-      <c r="J6" s="14" t="str">
+      <c r="J6" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Deaner_etal_2006_Table3</v>
       </c>
-      <c r="K6" s="14" t="str">
+      <c r="K6" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1177%2F147470490600400114_Table3</v>
       </c>
-      <c r="L6" s="14" t="str">
+      <c r="L6" s="12" t="str">
         <f t="array" ref="L6">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K6,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="10" t="s">
         <v>1422</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="10" t="s">
         <v>1423</v>
       </c>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12" t="s">
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T6" s="12" t="s">
+      <c r="T6" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12" t="s">
+      <c r="U6" s="10"/>
+      <c r="V6" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W6" s="11" t="s">
+      <c r="W6" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X6" s="12" t="s">
+      <c r="X6" s="10" t="s">
         <v>1424</v>
       </c>
-      <c r="Y6" s="12" t="s">
+      <c r="Y6" s="10" t="s">
         <v>1424</v>
       </c>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="11" t="s">
+      <c r="Z6" s="10"/>
+      <c r="AA6" s="10"/>
+      <c r="AB6" s="9" t="s">
         <v>1425</v>
       </c>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="11" t="s">
+      <c r="AC6" s="10"/>
+      <c r="AD6" s="10"/>
+      <c r="AE6" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF6" s="11"/>
-      <c r="AG6" s="8" t="s">
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="13" t="s">
         <v>1426</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>1427</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="11" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="14" t="str">
+      <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Reader</v>
       </c>
-      <c r="F7" s="14" t="str">
+      <c r="F7" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Laland</v>
       </c>
-      <c r="G7" s="14" t="str">
+      <c r="G7" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2002</v>
       </c>
-      <c r="H7" s="14" t="str">
+      <c r="H7" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Reader_Laland_2002</v>
       </c>
-      <c r="I7" s="14" t="str">
+      <c r="I7" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1073%2Fpnas.062041299</v>
       </c>
-      <c r="J7" s="14" t="str">
+      <c r="J7" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Reader_Laland_2002_Table1</v>
       </c>
-      <c r="K7" s="14" t="str">
+      <c r="K7" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1073%2Fpnas.062041299_Table1</v>
       </c>
-      <c r="L7" s="14" t="str">
+      <c r="L7" s="12" t="str">
         <f t="array" ref="L7">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K7,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="10" t="s">
         <v>1428</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="O7" s="10" t="s">
         <v>1429</v>
       </c>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12" t="s">
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10" t="s">
         <v>1430</v>
       </c>
-      <c r="S7" s="12" t="s">
+      <c r="S7" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T7" s="12" t="s">
+      <c r="T7" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12" t="s">
+      <c r="U7" s="10"/>
+      <c r="V7" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W7" s="11" t="s">
+      <c r="W7" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X7" s="12" t="s">
+      <c r="X7" s="10" t="s">
         <v>1431</v>
       </c>
-      <c r="Y7" s="12" t="s">
+      <c r="Y7" s="10" t="s">
         <v>1431</v>
       </c>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="12"/>
-      <c r="AB7" s="11" t="s">
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="9" t="s">
         <v>1432</v>
       </c>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="12"/>
-      <c r="AE7" s="11" t="s">
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF7" s="11"/>
-      <c r="AG7" s="8" t="s">
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="13" t="s">
         <v>1433</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>1434</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="11" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="14" t="str">
+      <c r="E8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Reader</v>
       </c>
-      <c r="F8" s="14" t="str">
+      <c r="F8" s="12" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="G8" s="14" t="str">
+      <c r="G8" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2011</v>
       </c>
-      <c r="H8" s="14" t="str">
+      <c r="H8" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Reader_etal_2011</v>
       </c>
-      <c r="I8" s="14" t="str">
+      <c r="I8" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1098%2Frstb.2010.0342</v>
       </c>
-      <c r="J8" s="14" t="str">
+      <c r="J8" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Reader_etal_2011_Table1</v>
       </c>
-      <c r="K8" s="14" t="str">
+      <c r="K8" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1098%2Frstb.2010.0342_Table1</v>
       </c>
-      <c r="L8" s="14" t="str">
+      <c r="L8" s="12" t="str">
         <f t="array" ref="L8">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K8,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="10" t="s">
         <v>1435</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O8" s="12" t="s">
+      <c r="O8" s="10" t="s">
         <v>1436</v>
       </c>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12" t="s">
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10" t="s">
         <v>1437</v>
       </c>
-      <c r="S8" s="12" t="s">
+      <c r="S8" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T8" s="12" t="s">
+      <c r="T8" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12" t="s">
+      <c r="U8" s="10"/>
+      <c r="V8" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W8" s="11" t="s">
+      <c r="W8" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X8" s="12" t="s">
+      <c r="X8" s="10" t="s">
         <v>1438</v>
       </c>
-      <c r="Y8" s="12" t="s">
+      <c r="Y8" s="10" t="s">
         <v>1438</v>
       </c>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="12"/>
-      <c r="AB8" s="11" t="s">
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="10"/>
+      <c r="AB8" s="9" t="s">
         <v>1439</v>
       </c>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="11" t="s">
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="10"/>
+      <c r="AE8" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF8" s="11"/>
-      <c r="AG8" s="8" t="s">
+      <c r="AF8" s="9"/>
+      <c r="AG8" s="13" t="s">
         <v>1440</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>1434</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="11" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="14" t="str">
+      <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Reader</v>
       </c>
-      <c r="F9" s="14" t="str">
+      <c r="F9" s="12" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="G9" s="14" t="str">
+      <c r="G9" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2011</v>
       </c>
-      <c r="H9" s="14" t="str">
+      <c r="H9" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Reader_etal_2011</v>
       </c>
-      <c r="I9" s="14" t="str">
+      <c r="I9" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1098%2Frstb.2010.0342</v>
       </c>
-      <c r="J9" s="14" t="str">
+      <c r="J9" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Reader_etal_2011_Table2</v>
       </c>
-      <c r="K9" s="14" t="str">
+      <c r="K9" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1098%2Frstb.2010.0342_Table2</v>
       </c>
-      <c r="L9" s="14" t="str">
+      <c r="L9" s="12" t="str">
         <f t="array" ref="L9">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K9,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="10" t="s">
         <v>1441</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O9" s="12" t="s">
+      <c r="O9" s="10" t="s">
         <v>1442</v>
       </c>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12" t="s">
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10" t="s">
         <v>1437</v>
       </c>
-      <c r="S9" s="12" t="s">
+      <c r="S9" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T9" s="12" t="s">
+      <c r="T9" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12" t="s">
+      <c r="U9" s="10"/>
+      <c r="V9" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W9" s="11" t="s">
+      <c r="W9" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X9" s="12" t="s">
+      <c r="X9" s="10" t="s">
         <v>1443</v>
       </c>
-      <c r="Y9" s="12" t="s">
+      <c r="Y9" s="10" t="s">
         <v>1443</v>
       </c>
-      <c r="Z9" s="12"/>
-      <c r="AA9" s="12"/>
-      <c r="AB9" s="11" t="s">
+      <c r="Z9" s="10"/>
+      <c r="AA9" s="10"/>
+      <c r="AB9" s="9" t="s">
         <v>1439</v>
       </c>
-      <c r="AC9" s="12"/>
-      <c r="AD9" s="12"/>
-      <c r="AE9" s="11" t="s">
+      <c r="AC9" s="10"/>
+      <c r="AD9" s="10"/>
+      <c r="AE9" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF9" s="11"/>
-      <c r="AG9" s="8" t="s">
+      <c r="AF9" s="9"/>
+      <c r="AG9" s="13" t="s">
         <v>1444</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="9" t="s">
         <v>1434</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="11" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="14" t="str">
+      <c r="E10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Reader</v>
       </c>
-      <c r="F10" s="14" t="str">
+      <c r="F10" s="12" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="G10" s="14" t="str">
+      <c r="G10" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2011</v>
       </c>
-      <c r="H10" s="14" t="str">
+      <c r="H10" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Reader_etal_2011</v>
       </c>
-      <c r="I10" s="14" t="str">
+      <c r="I10" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1098%2Frstb.2010.0342</v>
       </c>
-      <c r="J10" s="14" t="str">
+      <c r="J10" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Reader_etal_2011_Table3</v>
       </c>
-      <c r="K10" s="14" t="str">
+      <c r="K10" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1098%2Frstb.2010.0342_Table3</v>
       </c>
-      <c r="L10" s="14" t="str">
+      <c r="L10" s="12" t="str">
         <f t="array" ref="L10">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K10,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="10" t="s">
         <v>1445</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="N10" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="10" t="s">
         <v>1446</v>
       </c>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12" t="s">
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10" t="s">
         <v>1437</v>
       </c>
-      <c r="S10" s="12" t="s">
+      <c r="S10" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T10" s="12" t="s">
+      <c r="T10" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12" t="s">
+      <c r="U10" s="10"/>
+      <c r="V10" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W10" s="11" t="s">
+      <c r="W10" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X10" s="12" t="s">
+      <c r="X10" s="10" t="s">
         <v>1447</v>
       </c>
-      <c r="Y10" s="12" t="s">
+      <c r="Y10" s="10" t="s">
         <v>1447</v>
       </c>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="11" t="s">
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="9" t="s">
         <v>1448</v>
       </c>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="12"/>
-      <c r="AE10" s="11" t="s">
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF10" s="11"/>
-      <c r="AG10" s="8" t="s">
+      <c r="AF10" s="9"/>
+      <c r="AG10" s="13" t="s">
         <v>1449</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>1434</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="11" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="14" t="str">
+      <c r="E11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Reader</v>
       </c>
-      <c r="F11" s="14" t="str">
+      <c r="F11" s="12" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="G11" s="14" t="str">
+      <c r="G11" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2011</v>
       </c>
-      <c r="H11" s="14" t="str">
+      <c r="H11" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Reader_etal_2011</v>
       </c>
-      <c r="I11" s="14" t="str">
+      <c r="I11" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1098%2Frstb.2010.0342</v>
       </c>
-      <c r="J11" s="14" t="str">
+      <c r="J11" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Reader_etal_2011_Table4</v>
       </c>
-      <c r="K11" s="14" t="str">
+      <c r="K11" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1098%2Frstb.2010.0342_Table4</v>
       </c>
-      <c r="L11" s="14" t="str">
+      <c r="L11" s="12" t="str">
         <f t="array" ref="L11">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K11,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="10" t="s">
         <v>1450</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="O11" s="10" t="s">
         <v>1451</v>
       </c>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12" t="s">
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10" t="s">
         <v>1437</v>
       </c>
-      <c r="S11" s="12" t="s">
+      <c r="S11" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T11" s="12" t="s">
+      <c r="T11" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12" t="s">
+      <c r="U11" s="10"/>
+      <c r="V11" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W11" s="11" t="s">
+      <c r="W11" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X11" s="12" t="s">
+      <c r="X11" s="10" t="s">
         <v>1452</v>
       </c>
-      <c r="Y11" s="12" t="s">
+      <c r="Y11" s="10" t="s">
         <v>1452</v>
       </c>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12"/>
-      <c r="AB11" s="11" t="s">
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="9" t="s">
         <v>1415</v>
       </c>
-      <c r="AC11" s="12"/>
-      <c r="AD11" s="12"/>
-      <c r="AE11" s="11" t="s">
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF11" s="11"/>
-      <c r="AG11" s="8" t="s">
+      <c r="AF11" s="9"/>
+      <c r="AG11" s="13" t="s">
         <v>1453</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="9" t="s">
         <v>1454</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="11" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="14" t="str">
+      <c r="E12" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Shultz</v>
       </c>
-      <c r="F12" s="14" t="str">
+      <c r="F12" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Dunbar</v>
       </c>
-      <c r="G12" s="14" t="str">
+      <c r="G12" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2010</v>
       </c>
-      <c r="H12" s="14" t="str">
+      <c r="H12" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Shultz_Dunbar_2010</v>
       </c>
-      <c r="I12" s="14" t="str">
+      <c r="I12" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1037%2Fa0018894</v>
       </c>
-      <c r="J12" s="14" t="str">
+      <c r="J12" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Shultz_Dunbar_2010_Table1</v>
       </c>
-      <c r="K12" s="14" t="str">
+      <c r="K12" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1037%2Fa0018894_Table1</v>
       </c>
-      <c r="L12" s="14" t="str">
+      <c r="L12" s="12" t="str">
         <f t="array" ref="L12">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K12,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="10" t="s">
         <v>1455</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N12" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O12" s="12" t="s">
+      <c r="O12" s="10" t="s">
         <v>1456</v>
       </c>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12" t="s">
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="S12" s="12" t="s">
+      <c r="S12" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T12" s="12" t="s">
+      <c r="T12" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12" t="s">
+      <c r="U12" s="10"/>
+      <c r="V12" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W12" s="11" t="s">
+      <c r="W12" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X12" s="12" t="s">
+      <c r="X12" s="10" t="s">
         <v>1458</v>
       </c>
-      <c r="Y12" s="12" t="s">
+      <c r="Y12" s="10" t="s">
         <v>1458</v>
       </c>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
-      <c r="AB12" s="11" t="s">
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="9" t="s">
         <v>1459</v>
       </c>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="12"/>
-      <c r="AE12" s="11" t="s">
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF12" s="11"/>
-      <c r="AG12" s="8" t="s">
+      <c r="AF12" s="9"/>
+      <c r="AG12" s="13" t="s">
         <v>1460</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="9" t="s">
         <v>1454</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="11" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="14" t="str">
+      <c r="E13" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Shultz</v>
       </c>
-      <c r="F13" s="14" t="str">
+      <c r="F13" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Dunbar</v>
       </c>
-      <c r="G13" s="14" t="str">
+      <c r="G13" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2010</v>
       </c>
-      <c r="H13" s="14" t="str">
+      <c r="H13" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Shultz_Dunbar_2010</v>
       </c>
-      <c r="I13" s="14" t="str">
+      <c r="I13" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1037%2Fa0018894</v>
       </c>
-      <c r="J13" s="14" t="str">
+      <c r="J13" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Shultz_Dunbar_2010_Table2</v>
       </c>
-      <c r="K13" s="14" t="str">
+      <c r="K13" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1037%2Fa0018894_Table2</v>
       </c>
-      <c r="L13" s="14" t="str">
+      <c r="L13" s="12" t="str">
         <f t="array" ref="L13">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K13,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="10" t="s">
         <v>1461</v>
       </c>
-      <c r="N13" s="11" t="s">
+      <c r="N13" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="10" t="s">
         <v>1462</v>
       </c>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12" t="s">
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="S13" s="12" t="s">
+      <c r="S13" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T13" s="12" t="s">
+      <c r="T13" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12" t="s">
+      <c r="U13" s="10"/>
+      <c r="V13" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W13" s="11" t="s">
+      <c r="W13" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X13" s="12" t="s">
+      <c r="X13" s="10" t="s">
         <v>1463</v>
       </c>
-      <c r="Y13" s="12" t="s">
+      <c r="Y13" s="10" t="s">
         <v>1463</v>
       </c>
-      <c r="Z13" s="12"/>
-      <c r="AA13" s="12"/>
-      <c r="AB13" s="11" t="s">
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="9" t="s">
         <v>1464</v>
       </c>
-      <c r="AC13" s="12"/>
-      <c r="AD13" s="12"/>
-      <c r="AE13" s="11" t="s">
+      <c r="AC13" s="10"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF13" s="11"/>
-      <c r="AG13" s="8" t="s">
+      <c r="AF13" s="9"/>
+      <c r="AG13" s="13" t="s">
         <v>1465</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="9" t="s">
         <v>1454</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="11" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="14" t="str">
+      <c r="E14" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Shultz</v>
       </c>
-      <c r="F14" s="14" t="str">
+      <c r="F14" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Dunbar</v>
       </c>
-      <c r="G14" s="14" t="str">
+      <c r="G14" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2010</v>
       </c>
-      <c r="H14" s="14" t="str">
+      <c r="H14" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Shultz_Dunbar_2010</v>
       </c>
-      <c r="I14" s="14" t="str">
+      <c r="I14" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1037%2Fa0018894</v>
       </c>
-      <c r="J14" s="14" t="str">
+      <c r="J14" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Shultz_Dunbar_2010_Table3</v>
       </c>
-      <c r="K14" s="14" t="str">
+      <c r="K14" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1037%2Fa0018894_Table3</v>
       </c>
-      <c r="L14" s="14" t="str">
+      <c r="L14" s="12" t="str">
         <f t="array" ref="L14">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K14,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="10" t="s">
         <v>1466</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="O14" s="10" t="s">
         <v>1462</v>
       </c>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12" t="s">
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="S14" s="12" t="s">
+      <c r="S14" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T14" s="12" t="s">
+      <c r="T14" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12" t="s">
+      <c r="U14" s="10"/>
+      <c r="V14" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W14" s="11" t="s">
+      <c r="W14" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X14" s="12" t="s">
+      <c r="X14" s="10" t="s">
         <v>1467</v>
       </c>
-      <c r="Y14" s="12" t="s">
+      <c r="Y14" s="10" t="s">
         <v>1467</v>
       </c>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
-      <c r="AB14" s="11" t="s">
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="9" t="s">
         <v>1468</v>
       </c>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="12"/>
-      <c r="AE14" s="11" t="s">
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF14" s="11"/>
-      <c r="AG14" s="8" t="s">
+      <c r="AF14" s="9"/>
+      <c r="AG14" s="13" t="s">
         <v>1469</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="9" t="s">
         <v>1454</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="11" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="14" t="str">
+      <c r="E15" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Shultz</v>
       </c>
-      <c r="F15" s="14" t="str">
+      <c r="F15" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Dunbar</v>
       </c>
-      <c r="G15" s="14" t="str">
+      <c r="G15" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2010</v>
       </c>
-      <c r="H15" s="14" t="str">
+      <c r="H15" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Shultz_Dunbar_2010</v>
       </c>
-      <c r="I15" s="14" t="str">
+      <c r="I15" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1037%2Fa0018894</v>
       </c>
-      <c r="J15" s="14" t="str">
+      <c r="J15" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Shultz_Dunbar_2010_Table4</v>
       </c>
-      <c r="K15" s="14" t="str">
+      <c r="K15" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1037%2Fa0018894_Table4</v>
       </c>
-      <c r="L15" s="14" t="str">
+      <c r="L15" s="12" t="str">
         <f t="array" ref="L15">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K15,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="M15" s="10" t="s">
         <v>1470</v>
       </c>
-      <c r="N15" s="11" t="s">
+      <c r="N15" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O15" s="12" t="s">
+      <c r="O15" s="10" t="s">
         <v>1471</v>
       </c>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12" t="s">
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="S15" s="12" t="s">
+      <c r="S15" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T15" s="12" t="s">
+      <c r="T15" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12" t="s">
+      <c r="U15" s="10"/>
+      <c r="V15" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W15" s="11" t="s">
+      <c r="W15" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X15" s="12" t="s">
+      <c r="X15" s="10" t="s">
         <v>1472</v>
       </c>
-      <c r="Y15" s="12" t="s">
+      <c r="Y15" s="10" t="s">
         <v>1472</v>
       </c>
-      <c r="Z15" s="12"/>
-      <c r="AA15" s="12"/>
-      <c r="AB15" s="11" t="s">
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="9" t="s">
         <v>1448</v>
       </c>
-      <c r="AC15" s="12"/>
-      <c r="AD15" s="12"/>
-      <c r="AE15" s="11" t="s">
+      <c r="AC15" s="10"/>
+      <c r="AD15" s="10"/>
+      <c r="AE15" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF15" s="11"/>
-      <c r="AG15" s="8" t="s">
+      <c r="AF15" s="9"/>
+      <c r="AG15" s="13" t="s">
         <v>1469</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="9" t="s">
         <v>1454</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="11" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="14" t="str">
+      <c r="E16" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Shultz</v>
       </c>
-      <c r="F16" s="14" t="str">
+      <c r="F16" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Dunbar</v>
       </c>
-      <c r="G16" s="14" t="str">
+      <c r="G16" s="12" t="str">
         <f t="shared" si="2"/>
         <v>2010</v>
       </c>
-      <c r="H16" s="14" t="str">
+      <c r="H16" s="12" t="str">
         <f t="shared" si="3"/>
         <v>Shultz_Dunbar_2010</v>
       </c>
-      <c r="I16" s="14" t="str">
+      <c r="I16" s="12" t="str">
         <f t="shared" si="4"/>
         <v>10.1037%2Fa0018894</v>
       </c>
-      <c r="J16" s="14" t="str">
+      <c r="J16" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Shultz_Dunbar_2010_Table5</v>
       </c>
-      <c r="K16" s="14" t="str">
+      <c r="K16" s="12" t="str">
         <f t="shared" si="6"/>
         <v>10.1037%2Fa0018894_Table5</v>
       </c>
-      <c r="L16" s="14" t="str">
+      <c r="L16" s="12" t="str">
         <f t="array" ref="L16">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K16,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="10" t="s">
         <v>1473</v>
       </c>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="9" t="s">
         <v>1400</v>
       </c>
-      <c r="O16" s="12" t="s">
+      <c r="O16" s="10" t="s">
         <v>1474</v>
       </c>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12" t="s">
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="S16" s="12" t="s">
+      <c r="S16" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="T16" s="12" t="s">
+      <c r="T16" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12" t="s">
+      <c r="U16" s="10"/>
+      <c r="V16" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="W16" s="11" t="s">
+      <c r="W16" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X16" s="12" t="s">
+      <c r="X16" s="10" t="s">
         <v>1472</v>
       </c>
-      <c r="Y16" s="12" t="s">
+      <c r="Y16" s="10" t="s">
         <v>1472</v>
       </c>
-      <c r="Z16" s="12"/>
-      <c r="AA16" s="12"/>
-      <c r="AB16" s="11" t="s">
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="9" t="s">
         <v>1475</v>
       </c>
-      <c r="AC16" s="12"/>
-      <c r="AD16" s="12"/>
-      <c r="AE16" s="11" t="s">
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AF16" s="11"/>
-      <c r="AG16" s="8" t="s">
+      <c r="AF16" s="9"/>
+      <c r="AG16" s="13" t="s">
         <v>1476</v>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>1477</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="6" t="str">
         <f t="shared" si="0"/>
         <v>Weaver</v>
@@ -45474,21 +45474,21 @@
         <f t="array" ref="L17">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K17,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="M17" s="10"/>
-      <c r="O17" s="10" t="s">
+      <c r="M17" s="8"/>
+      <c r="O17" s="8" t="s">
         <v>1478</v>
       </c>
-      <c r="P17" s="8"/>
+      <c r="P17" s="13"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -46933,256 +46933,271 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>2105</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>2107</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>2138</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
         <v>2155</v>
       </c>
     </row>
@@ -47468,13 +47483,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB8D63A6-4950-4037-89AC-A09843539280}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60966FE0-C5F0-4145-9213-43D4E7FD46A5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E272D686-4E28-47F9-B7CC-BCB6EC7B2ADB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42F54CF2-B092-4329-8B8E-3E0FB6E0CCA6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51763920-0C34-431F-8EBD-51B47BAF59BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6544658-4383-41DD-AD5C-A5A5ED333778}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -54779,4 +54779,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{667A62BD-8058-49B9-BCED-170AEB959EB2}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D07CB52E-A903-462D-88F5-9B22F2BF942F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EABCD842-844A-4E96-9A5F-E02EE74C9F41}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -51334,4 +51334,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CAFE56D-C2BB-4071-9445-AA4D8E7C1776}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97754777-9E3C-4733-90C0-908502FAAA46}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E299D75F-8101-46EF-94B1-D8039C2DF94E}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -51427,4 +51427,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB76B97C-9781-4EDA-A29B-89FD91BB00E7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79F4C688-D38E-4E6F-95B6-76B648BF5332}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A9CEF21-AF10-4F42-B570-FE50FD225D85}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_FFD271E7C4A475BD4A9BFB05E8F0A690F9029ADD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A426303-6EB8-447B-A895-5BD4203C7D45}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_FFD271E7C4A475BD4A9BFB05E8F0A690F9029ADD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0919565E-E4F4-4B50-AB8C-6208A2A2C94C}"/>
   <bookViews>
     <workbookView xWindow="51020" yWindow="-5860" windowWidth="33480" windowHeight="26820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5965" uniqueCount="2491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5975" uniqueCount="2491">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -57457,6 +57457,9 @@
       <c r="A500" t="s">
         <v>1772</v>
       </c>
+      <c r="B500" t="s">
+        <v>283</v>
+      </c>
       <c r="D500" t="s">
         <v>81</v>
       </c>
@@ -57496,7 +57499,7 @@
       </c>
       <c r="H500" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Heffner_Heffner_2010</v>
+        <v>Heffner_Heffner_2010_b</v>
       </c>
       <c r="I500" s="12" t="str">
         <f t="shared" si="101"/>
@@ -57504,7 +57507,7 @@
       </c>
       <c r="J500" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_Heffner_2010_Table1</v>
+        <v>Heffner_Heffner_2010_b_Table1</v>
       </c>
       <c r="K500" s="13" t="str">
         <f t="shared" si="103"/>
@@ -57563,6 +57566,9 @@
     <row r="501" spans="1:33" ht="15" customHeight="1">
       <c r="A501" t="s">
         <v>1781</v>
+      </c>
+      <c r="B501" t="s">
+        <v>278</v>
       </c>
       <c r="D501" t="s">
         <v>529</v>
@@ -57603,7 +57609,7 @@
       </c>
       <c r="H501" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Heffner_etal_1994</v>
+        <v>Heffner_etal_1994_a</v>
       </c>
       <c r="I501" s="12" t="str">
         <f t="shared" si="101"/>
@@ -57611,7 +57617,7 @@
       </c>
       <c r="J501" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_etal_1994_Figure2</v>
+        <v>Heffner_etal_1994_a_Figure2</v>
       </c>
       <c r="K501" s="13" t="str">
         <f t="shared" si="103"/>
@@ -57667,6 +57673,9 @@
     <row r="502" spans="1:33" ht="15" customHeight="1">
       <c r="A502" t="s">
         <v>1781</v>
+      </c>
+      <c r="B502" t="s">
+        <v>278</v>
       </c>
       <c r="D502" t="s">
         <v>628</v>
@@ -57707,7 +57716,7 @@
       </c>
       <c r="H502" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Heffner_etal_1994</v>
+        <v>Heffner_etal_1994_a</v>
       </c>
       <c r="I502" s="12" t="str">
         <f t="shared" si="101"/>
@@ -57715,7 +57724,7 @@
       </c>
       <c r="J502" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_etal_1994_Figure1</v>
+        <v>Heffner_etal_1994_a_Figure1</v>
       </c>
       <c r="K502" s="13" t="str">
         <f t="shared" si="103"/>
@@ -57771,6 +57780,9 @@
     <row r="503" spans="1:33" ht="15" customHeight="1">
       <c r="A503" t="s">
         <v>1789</v>
+      </c>
+      <c r="B503" t="s">
+        <v>283</v>
       </c>
       <c r="D503" t="s">
         <v>330</v>
@@ -57811,7 +57823,7 @@
       </c>
       <c r="H503" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Heffner_etal_1994</v>
+        <v>Heffner_etal_1994_b</v>
       </c>
       <c r="I503" s="12" t="str">
         <f t="shared" si="101"/>
@@ -57819,7 +57831,7 @@
       </c>
       <c r="J503" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_etal_1994_Figure3</v>
+        <v>Heffner_etal_1994_b_Figure3</v>
       </c>
       <c r="K503" s="13" t="str">
         <f t="shared" si="103"/>
@@ -57881,6 +57893,9 @@
     <row r="504" spans="1:33" ht="15" customHeight="1">
       <c r="A504" t="s">
         <v>1796</v>
+      </c>
+      <c r="B504" t="s">
+        <v>695</v>
       </c>
       <c r="D504" t="s">
         <v>81</v>
@@ -57921,7 +57936,7 @@
       </c>
       <c r="H504" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Heffner_etal_1994</v>
+        <v>Heffner_etal_1994_c</v>
       </c>
       <c r="I504" s="12" t="str">
         <f t="shared" si="101"/>
@@ -57929,7 +57944,7 @@
       </c>
       <c r="J504" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_etal_1994_Table1</v>
+        <v>Heffner_etal_1994_c_Table1</v>
       </c>
       <c r="K504" s="13" t="str">
         <f t="shared" si="103"/>
@@ -57991,6 +58006,9 @@
     <row r="505" spans="1:33" ht="15" customHeight="1">
       <c r="A505" t="s">
         <v>1796</v>
+      </c>
+      <c r="B505" t="s">
+        <v>695</v>
       </c>
       <c r="D505" t="s">
         <v>1131</v>
@@ -58031,7 +58049,7 @@
       </c>
       <c r="H505" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Heffner_etal_1994</v>
+        <v>Heffner_etal_1994_c</v>
       </c>
       <c r="I505" s="12" t="str">
         <f t="shared" si="101"/>
@@ -58039,7 +58057,7 @@
       </c>
       <c r="J505" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_etal_1994_Figure7</v>
+        <v>Heffner_etal_1994_c_Figure7</v>
       </c>
       <c r="K505" s="13" t="str">
         <f t="shared" si="103"/>
@@ -59368,6 +59386,9 @@
       <c r="A518" t="s">
         <v>1873</v>
       </c>
+      <c r="B518" t="s">
+        <v>283</v>
+      </c>
       <c r="D518" t="s">
         <v>1750</v>
       </c>
@@ -59407,7 +59428,7 @@
       </c>
       <c r="H518" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Koay_etal_1998</v>
+        <v>Koay_etal_1998_b</v>
       </c>
       <c r="I518" s="12" t="str">
         <f t="shared" si="101"/>
@@ -59415,7 +59436,7 @@
       </c>
       <c r="J518" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Koay_etal_1998_Resultstext</v>
+        <v>Koay_etal_1998_b_Resultstext</v>
       </c>
       <c r="K518" s="13" t="str">
         <f t="shared" si="103"/>
@@ -59474,6 +59495,9 @@
     <row r="519" spans="1:33" ht="15" customHeight="1">
       <c r="A519" t="s">
         <v>1873</v>
+      </c>
+      <c r="B519" t="s">
+        <v>283</v>
       </c>
       <c r="D519" t="s">
         <v>1882</v>
@@ -59514,7 +59538,7 @@
       </c>
       <c r="H519" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Koay_etal_1998</v>
+        <v>Koay_etal_1998_b</v>
       </c>
       <c r="I519" s="12" t="str">
         <f t="shared" si="101"/>
@@ -59522,7 +59546,7 @@
       </c>
       <c r="J519" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Koay_etal_1998_Figure8</v>
+        <v>Koay_etal_1998_b_Figure8</v>
       </c>
       <c r="K519" s="13" t="str">
         <f t="shared" si="103"/>
@@ -59584,6 +59608,9 @@
     <row r="520" spans="1:33" ht="15" customHeight="1">
       <c r="A520" t="s">
         <v>1873</v>
+      </c>
+      <c r="B520" t="s">
+        <v>283</v>
       </c>
       <c r="D520" t="s">
         <v>1867</v>
@@ -59624,7 +59651,7 @@
       </c>
       <c r="H520" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Koay_etal_1998</v>
+        <v>Koay_etal_1998_b</v>
       </c>
       <c r="I520" s="12" t="str">
         <f t="shared" si="101"/>
@@ -59632,7 +59659,7 @@
       </c>
       <c r="J520" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Koay_etal_1998_Figure9</v>
+        <v>Koay_etal_1998_b_Figure9</v>
       </c>
       <c r="K520" s="13" t="str">
         <f t="shared" si="103"/>
@@ -60189,7 +60216,7 @@
         <v>1909</v>
       </c>
       <c r="D526" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E526" s="12" t="str">
         <f t="shared" si="98"/>
@@ -60235,11 +60262,11 @@
       </c>
       <c r="J526" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Dalland__1965_Resultstext</v>
+        <v>Dalland__1965_ResultsText</v>
       </c>
       <c r="K526" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1126%2Fscience.150.3700.1185_Resultstext</v>
+        <v>10.1126%2Fscience.150.3700.1185_ResultsText</v>
       </c>
       <c r="L526" s="13" t="str">
         <f t="array" ref="L526">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K526,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -60340,7 +60367,7 @@
         <v>1915</v>
       </c>
       <c r="D528" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E528" s="12" t="str">
         <f t="shared" si="98"/>
@@ -60386,11 +60413,11 @@
       </c>
       <c r="J528" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Gillette_etal_1973_Resultstext</v>
+        <v>Gillette_etal_1973_ResultsText</v>
       </c>
       <c r="K528" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>PMID%3A4689764_Resultstext</v>
+        <v>PMID%3A4689764_ResultsText</v>
       </c>
       <c r="L528" s="13" t="str">
         <f t="array" ref="L528">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K528,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -60417,7 +60444,7 @@
         <v>1919</v>
       </c>
       <c r="D529" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E529" s="12" t="str">
         <f t="shared" si="98"/>
@@ -60463,11 +60490,11 @@
       </c>
       <c r="J529" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_etal_1969_Resultstext</v>
+        <v>Heffner_etal_1969_ResultsText</v>
       </c>
       <c r="K529" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>AN%3A1970-12222-001_Resultstext</v>
+        <v>AN%3A1970-12222-001_ResultsText</v>
       </c>
       <c r="L529" s="13" t="str">
         <f t="array" ref="L529">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K529,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -60491,7 +60518,7 @@
         <v>1922</v>
       </c>
       <c r="D530" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E530" s="12" t="str">
         <f t="shared" si="98"/>
@@ -60537,11 +60564,11 @@
       </c>
       <c r="J530" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_etal_2001_Resultstext</v>
+        <v>Heffner_etal_2001_ResultsText</v>
       </c>
       <c r="K530" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1016%2FS0378-5955(01)00298-2_Resultstext</v>
+        <v>10.1016%2FS0378-5955(01)00298-2_ResultsText</v>
       </c>
       <c r="L530" s="13" t="str">
         <f t="array" ref="L530">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K530,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -60565,7 +60592,7 @@
         <v>1924</v>
       </c>
       <c r="D531" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E531" s="12" t="str">
         <f t="shared" si="98"/>
@@ -60611,11 +60638,11 @@
       </c>
       <c r="J531" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_etal_2006_Resultstext</v>
+        <v>Heffner_etal_2006_ResultsText</v>
       </c>
       <c r="K531" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1016%2Fj.heares.2006.06.008_Resultstext</v>
+        <v>10.1016%2Fj.heares.2006.06.008_ResultsText</v>
       </c>
       <c r="L531" s="13" t="str">
         <f t="array" ref="L531">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K531,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -60787,7 +60814,7 @@
         <v>1933</v>
       </c>
       <c r="D534" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E534" s="12" t="str">
         <f t="shared" si="98"/>
@@ -60833,11 +60860,11 @@
       </c>
       <c r="J534" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Heffner_Heffner_1982_Resultstext</v>
+        <v>Heffner_Heffner_1982_ResultsText</v>
       </c>
       <c r="K534" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1037%2F0735-7036.96.6.926_Resultstext</v>
+        <v>10.1037%2F0735-7036.96.6.926_ResultsText</v>
       </c>
       <c r="L534" s="13" t="str">
         <f t="array" ref="L534">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K534,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -61009,7 +61036,7 @@
         <v>1943</v>
       </c>
       <c r="D537" s="14" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E537" s="12" t="str">
         <f t="shared" si="98"/>
@@ -61055,11 +61082,11 @@
       </c>
       <c r="J537" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Jackson_etal_1997_Resultstext</v>
+        <v>Jackson_etal_1997_ResultsText</v>
       </c>
       <c r="K537" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1037%2F0735-7036.111.1.100_Resultstext</v>
+        <v>10.1037%2F0735-7036.111.1.100_ResultsText</v>
       </c>
       <c r="L537" s="13" t="str">
         <f t="array" ref="L537">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K537,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -61175,7 +61202,7 @@
         <v>1949</v>
       </c>
       <c r="D539" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E539" s="12" t="str">
         <f t="shared" si="98"/>
@@ -61221,11 +61248,11 @@
       </c>
       <c r="J539" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Kastak_Schusterman_1999_Resultstext</v>
+        <v>Kastak_Schusterman_1999_ResultsText</v>
       </c>
       <c r="K539" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1139%2Fz99-151_Resultstext</v>
+        <v>10.1139%2Fz99-151_ResultsText</v>
       </c>
       <c r="L539" s="13" t="str">
         <f t="array" ref="L539">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K539,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -61247,6 +61274,9 @@
     <row r="540" spans="1:31" ht="15">
       <c r="A540" t="s">
         <v>1951</v>
+      </c>
+      <c r="B540" t="s">
+        <v>283</v>
       </c>
       <c r="D540" t="s">
         <v>568</v>
@@ -61287,7 +61317,7 @@
       </c>
       <c r="H540" s="12" t="str">
         <f t="shared" si="100"/>
-        <v>Kastelein_etal_2010</v>
+        <v>Kastelein_etal_2010_b</v>
       </c>
       <c r="I540" s="12" t="str">
         <f t="shared" si="101"/>
@@ -61295,7 +61325,7 @@
       </c>
       <c r="J540" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Kastelein_etal_2010_TableI</v>
+        <v>Kastelein_etal_2010_b_TableI</v>
       </c>
       <c r="K540" s="13" t="str">
         <f t="shared" si="103"/>
@@ -61323,7 +61353,7 @@
         <v>1953</v>
       </c>
       <c r="D541" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E541" s="12" t="str">
         <f t="shared" si="98"/>
@@ -61369,11 +61399,11 @@
       </c>
       <c r="J541" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Kelly_etal_1986_Resultstext</v>
+        <v>Kelly_etal_1986_ResultsText</v>
       </c>
       <c r="K541" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1016%2F0378-5955(86)90025-0_Resultstext</v>
+        <v>10.1016%2F0378-5955(86)90025-0_ResultsText</v>
       </c>
       <c r="L541" s="13" t="str">
         <f t="array" ref="L541">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K541,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -61397,7 +61427,7 @@
         <v>1955</v>
       </c>
       <c r="D542" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E542" s="12" t="str">
         <f t="shared" si="98"/>
@@ -61443,11 +61473,11 @@
       </c>
       <c r="J542" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Koay_etal_2003_Resultstext</v>
+        <v>Koay_etal_2003_ResultsText</v>
       </c>
       <c r="K542" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1016%2FS0378-5955(03)00025-X_Resultstext</v>
+        <v>10.1016%2FS0378-5955(03)00025-X_ResultsText</v>
       </c>
       <c r="L542" s="13" t="str">
         <f t="array" ref="L542">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K542,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -61625,7 +61655,7 @@
         <v>1966</v>
       </c>
       <c r="D545" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E545" s="12" t="str">
         <f t="shared" si="98"/>
@@ -61671,11 +61701,11 @@
       </c>
       <c r="J545" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Ravizza_etal_1969_Resultstext</v>
+        <v>Ravizza_etal_1969_ResultsText</v>
       </c>
       <c r="K545" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>AN%3A1970-12227-001_Resultstext</v>
+        <v>AN%3A1970-12227-001_ResultsText</v>
       </c>
       <c r="L545" s="13" t="str">
         <f t="array" ref="L545">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K545,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -61699,7 +61729,7 @@
         <v>1969</v>
       </c>
       <c r="D546" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E546" s="12" t="str">
         <f t="shared" si="98"/>
@@ -61745,11 +61775,11 @@
       </c>
       <c r="J546" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Ravizza_Masterton_1972_Resultstext</v>
+        <v>Ravizza_Masterton_1972_ResultsText</v>
       </c>
       <c r="K546" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1152%2Fjn.1972.35.3.344_Resultstext</v>
+        <v>10.1152%2Fjn.1972.35.3.344_ResultsText</v>
       </c>
       <c r="L546" s="13" t="str">
         <f t="array" ref="L546">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K546,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -61921,7 +61951,7 @@
         <v>1977</v>
       </c>
       <c r="D549" t="s">
-        <v>1750</v>
+        <v>362</v>
       </c>
       <c r="E549" s="12" t="str">
         <f t="shared" si="98"/>
@@ -61967,11 +61997,11 @@
       </c>
       <c r="J549" s="12" t="str">
         <f t="shared" si="102"/>
-        <v>Schusterman_Moore_1980_Resultstext</v>
+        <v>Schusterman_Moore_1980_ResultsText</v>
       </c>
       <c r="K549" s="13" t="str">
         <f t="shared" si="103"/>
-        <v>10.1121%2F1.2004876_Resultstext</v>
+        <v>10.1121%2F1.2004876_ResultsText</v>
       </c>
       <c r="L549" s="13" t="str">
         <f t="array" ref="L549">IFERROR(INDEX(AUTO_Public_TSV_FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(K549,IFERROR(_xlfn.TEXTBEFORE(AUTO_Public_TSV_FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -67126,14 +67156,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -67392,16 +67420,18 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA8EC149-61AF-4B66-8CE7-FC1A1EC48828}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EDDDE71-F6EC-4715-A2D1-C6B6331305A2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -67409,5 +67439,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EDDDE71-F6EC-4715-A2D1-C6B6331305A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA8EC149-61AF-4B66-8CE7-FC1A1EC48828}"/>
 </file>